--- a/public/templates/office/Phase0_3개년_TCO_원가계산서.xlsx
+++ b/public/templates/office/Phase0_3개년_TCO_원가계산서.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3개년_TCO_원가계산" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_3개년_TCO_총괄표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +30,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +47,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +66,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,27 +116,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,32 +538,31 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3개년_TCO_원가계산</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>[EMP-XLS-P0-04] SyncGuard AI 3개년 총소유비용(TCO) 및 구축 원가계산서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>초기 구축비(4.5억 원) 및 2~3차년도 클라우드·AI 토큰(FinOps)·유지관리 통합 TCO 산출서 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>비목 분류</t>
@@ -519,7 +570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>세부 항목</t>
+          <t>세부 산출 항목 (SyncGuard AI 기준)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -534,17 +585,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1차년도(구축)</t>
+          <t>1차년도 (구축)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2차년도(운영)</t>
+          <t>2차년도 (운영)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>3차년도(운영)</t>
+          <t>3차년도 (운영)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -554,364 +605,359 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>비고 및 산출 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>산출 근거 및 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>인건비(구축)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>PM / 프로젝트 총괄</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>6 M/M</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E5" s="4">
-        <f>C5*D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>사업총괄 PM / AI 수석 아키텍트 (특급 2명)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>8 M/M</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <f>SUM(E5:G5)</f>
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>초기 구축 6개월 투입</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>SW기술자 노임단가 및 6개월 구축 투입</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>인건비(구축)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>수석 아키텍트 (TL)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>6 M/M</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AI·백엔드·프론트엔드 PL (고급 2명)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>8 M/M</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>11000000</v>
       </c>
-      <c r="E6" s="6">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="E6" s="12" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
         <f>SUM(E6:G6)</f>
         <v/>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>아키텍처 및 코어 설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>멀티모달 RAG 파이프라인 및 FO/BO 웹 구현</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>인건비(구축)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>풀스택 / AI 개발자</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>18 M/M</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>데이터·QA 엔지니어 및 정규식 튜닝 (중급 2명)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>4 M/M</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>8500000</v>
       </c>
-      <c r="E7" s="4">
-        <f>C7*D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="E7" s="7" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <f>SUM(E7:G7)</f>
         <v/>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>백엔드/프론트엔드 페어 개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>인건비(운영)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>전담 유지보수 엔지니어</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>12 M/M</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>72000000</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>75600000</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>100대 규제 룰셋, 골든셋 50문항 및 품질 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>외주도급비</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>기간계(ProductLab·MarketingHub·SSO) 연계 어댑터</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>1 식</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
         <f>SUM(E8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>2, 3차년도 연간 유지보수(5% 인상)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>승인 협력사 ㈜데이터브릿지 전문 도급</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>하드웨어</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>온프레미스 GPU 서버(L40S)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>2 대</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="H9" s="4">
+          <t>솔루션·제경비</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>SyncSeries AI 코어 엔진 라이선스 및 기술료·부가세</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>1 식</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <f>SUM(E9:G9)</f>
         <v/>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>3년 감가상각 및 하드웨어 유지보수</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>클라우드/인프라</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>클라우드 호스팅 / 트래픽</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>1차년도 구축 계약 총액: 450,000,000원 (VAT 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>유지보수비</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>응용SW 및 AI 파이프라인 연간 유지관리 (2차년도 유상)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>12 개월</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>25200000</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>26460000</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="D10" s="12" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="H10" s="12">
         <f>SUM(E10:G10)</f>
         <v/>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>AWS/GCP 인프라 비용 (연 5% 증가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>1차년도 무상 하자보수, 2~3차년도 연 12% SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>AI 토큰비</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>상용 LLM API 토큰 소비</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+          <t>클라우드인프라</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AWS EKS, RDS PostgreSQL 16(Multi-AZ), S3, ALB</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>12 개월</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="D11" s="7" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>16800000</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>35280000</v>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(E11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>한빛글로벌 AWS 계정 직접 과금 (RI 약정 할인 반영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>AI FinOps</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-4o / Claude 3.5 / Clova OCR API 토큰 실비</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>12 개월</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>21600000</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>25920000</v>
-      </c>
-      <c r="H11" s="4">
-        <f>SUM(E11:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>월 150만원 기준 종량제 실비</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>라이선스</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 솔루션 영구라이선스</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1 식</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="G12" s="12" t="n">
+        <v>23760000</v>
+      </c>
+      <c r="H12" s="12">
         <f>SUM(E12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>SyncSeries 코어 라이선스 및 10% 유지비</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>월평균 심의 3,500건 기준 (Redis 시맨틱 캐시 42% 절감 반영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>총 소유비용(TCO) 총계</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>3개년 총소유비용 (Total Cost of Ownership)</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
         <f>SUM(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="17">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="17">
         <f>SUM(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="17">
         <f>SUM(H5:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>3개년 총 투자 비용 산출 완료</t>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>연간 수기 심의 외주·법무 검토 절감액(연 3.8억) 대비 ROI 14개월 달성</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/office/Phase0_3개년_TCO_원가계산서.xlsx
+++ b/public/templates/office/Phase0_3개년_TCO_원가계산서.xlsx
@@ -551,7 +551,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P0-04] SyncGuard AI 3개년 총소유비용(TCO) 및 구축 원가계산서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P0-04] SyncFlow AI 3개년 총소유비용(TCO) 및 구축 원가계산서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>세부 산출 항목 (SyncGuard AI 기준)</t>
+          <t>세부 산출 항목 (SyncFlow AI 기준)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>기간계(ProductLab·MarketingHub·SSO) 연계 어댑터</t>
+          <t>기간계(PLM-Nexus·SRM-Portal·SSO) 연계 어댑터</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>OpenAI GPT-4o / Claude 3.5 / Clova OCR API 토큰 실비</t>
+          <t>OpenAI GPT-4o / Claude 3.5 / Enterprise Vision OCR API 토큰 실비</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>월평균 심의 3,500건 기준 (Redis 시맨틱 캐시 42% 절감 반영)</t>
+          <t>월평균 검증 3,500건 기준 (Redis 시맨틱 캐시 42% 절감 반영)</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>연간 수기 심의 외주·법무 검토 절감액(연 3.8억) 대비 ROI 14개월 달성</t>
+          <t>연간 수기 검증 외주·법무 검토 절감액(연 3.8억) 대비 ROI 14개월 달성</t>
         </is>
       </c>
     </row>
